--- a/$/Money.xlsx
+++ b/$/Money.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tro\$\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738FF77B-87B6-4043-8127-A3B3A3A8E435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E309262-BEC0-4CBA-A084-698211731E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Phòng</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Check</t>
-  </si>
-  <si>
-    <t>Tháng 08 - 2026</t>
   </si>
 </sst>
 </file>
@@ -183,14 +180,8 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -209,6 +200,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -491,1266 +488,630 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="E4:N43"/>
+  <dimension ref="E4:N22"/>
   <sheetFormatPr defaultColWidth="13.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="5:14" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="4"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="2"/>
     </row>
     <row r="5" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
+      <c r="E5" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1" t="s">
+      <c r="L5" s="10"/>
+      <c r="M5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
     </row>
     <row r="7" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>103</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
         <v>2500000</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="4">
         <v>2542</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>3000</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <f>IF(H7-G7 &gt; 0, H7-G7, 0)</f>
         <v>458</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <f>I7*3000</f>
         <v>1374000</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="4">
         <v>1</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="7">
         <f>K7*110000</f>
         <v>110000</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="8">
         <f>F7+J7+L7</f>
         <v>3984000</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="4">
         <v>2500000</v>
       </c>
     </row>
     <row r="8" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>104</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="7">
         <v>3200000</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>3736</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4">
         <f t="shared" ref="I8:I20" si="0">IF(H8-G8 &gt; 0, H8-G8, 0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="7">
         <f t="shared" ref="J8:J20" si="1">I8*3000</f>
         <v>0</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="4">
         <v>1</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="7">
         <f t="shared" ref="L8:L20" si="2">K8*110000</f>
         <v>110000</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="8">
         <f t="shared" ref="M8:M20" si="3">F8+J8+L8</f>
         <v>3310000</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="4">
         <v>3000000</v>
       </c>
     </row>
     <row r="9" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <v>201</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="7">
         <v>3000000</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>5894</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="4">
         <v>2</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="7">
         <f t="shared" si="2"/>
         <v>220000</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="8">
         <f t="shared" si="3"/>
         <v>3220000</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="4">
         <v>2800000</v>
       </c>
     </row>
     <row r="10" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E10" s="5">
+      <c r="E10" s="3">
         <v>202</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="7">
         <v>2800000</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="4">
         <v>5826</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6">
+      <c r="H10" s="4"/>
+      <c r="I10" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="4">
         <v>2</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="7">
         <f t="shared" si="2"/>
         <v>220000</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="8">
         <f t="shared" si="3"/>
         <v>3020000</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="4">
         <v>2800000</v>
       </c>
     </row>
     <row r="11" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E11" s="5">
+      <c r="E11" s="3">
         <v>203</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="7">
         <v>3000000</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="4">
         <v>7113</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6">
+      <c r="H11" s="4"/>
+      <c r="I11" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="4">
         <v>1</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="7">
         <f t="shared" si="2"/>
         <v>110000</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="8">
         <f t="shared" si="3"/>
         <v>3110000</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="4">
         <v>3000000</v>
       </c>
     </row>
     <row r="12" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E12" s="5">
+      <c r="E12" s="3">
         <v>204</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="7">
         <v>3200000</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="4">
         <v>14308</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6">
+      <c r="H12" s="4"/>
+      <c r="I12" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="4">
         <v>2</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="7">
         <f t="shared" si="2"/>
         <v>220000</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="8">
         <f t="shared" si="3"/>
         <v>3420000</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="4">
         <v>2800000</v>
       </c>
     </row>
     <row r="13" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E13" s="5">
+      <c r="E13" s="3">
         <v>301</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="7">
         <v>3100000</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="4">
         <v>6034</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="4">
         <v>1</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="7">
         <f t="shared" si="2"/>
         <v>110000</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="8">
         <f t="shared" si="3"/>
         <v>3210000</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="4">
         <v>3100000</v>
       </c>
     </row>
     <row r="14" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <v>302</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="7">
         <v>2900000</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="4">
         <v>6821</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6">
+      <c r="H14" s="4"/>
+      <c r="I14" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="4">
         <v>1</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="7">
         <f t="shared" si="2"/>
         <v>110000</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="8">
         <f t="shared" si="3"/>
         <v>3010000</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="4">
         <v>2900000</v>
       </c>
     </row>
     <row r="15" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E15" s="5">
+      <c r="E15" s="3">
         <v>303</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="7">
         <v>3000000</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="4">
         <v>7758</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6">
+      <c r="H15" s="4"/>
+      <c r="I15" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="4">
         <v>2</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="7">
         <f t="shared" si="2"/>
         <v>220000</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="8">
         <f t="shared" si="3"/>
         <v>3220000</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="4">
         <v>3000000</v>
       </c>
     </row>
     <row r="16" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E16" s="5">
+      <c r="E16" s="3">
         <v>304</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="7">
         <v>2900000</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="4">
         <v>6688</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6">
+      <c r="H16" s="4"/>
+      <c r="I16" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="4">
         <v>1</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="7">
         <f t="shared" si="2"/>
         <v>110000</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="8">
         <f t="shared" si="3"/>
         <v>3010000</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="4">
         <v>2500000</v>
       </c>
     </row>
     <row r="17" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E17" s="5">
+      <c r="E17" s="3">
         <v>401</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="7">
         <v>3000000</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="4">
         <v>1763</v>
       </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6">
+      <c r="H17" s="4"/>
+      <c r="I17" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="4">
         <v>2</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="7">
         <f t="shared" si="2"/>
         <v>220000</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="8">
         <f t="shared" si="3"/>
         <v>3220000</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="4">
         <v>2500000</v>
       </c>
     </row>
     <row r="18" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E18" s="5">
+      <c r="E18" s="3">
         <v>402</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="7">
         <v>2800000</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="4">
         <v>5359</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6">
+      <c r="H18" s="4"/>
+      <c r="I18" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="4">
         <v>1</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="7">
         <f t="shared" si="2"/>
         <v>110000</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="8">
         <f t="shared" si="3"/>
         <v>2910000</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="4">
         <v>2800000</v>
       </c>
     </row>
     <row r="19" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E19" s="5">
+      <c r="E19" s="3">
         <v>403</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="7">
         <v>2900000</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="4">
         <v>609</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6">
+      <c r="H19" s="4"/>
+      <c r="I19" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="4">
         <v>2</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="7">
         <f t="shared" si="2"/>
         <v>220000</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="8">
         <f t="shared" si="3"/>
         <v>3120000</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="4">
         <v>2300000</v>
       </c>
     </row>
     <row r="20" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E20" s="5">
+      <c r="E20" s="3">
         <v>404</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="7">
         <v>2900000</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="4">
         <v>6993</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6">
+      <c r="H20" s="4"/>
+      <c r="I20" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="4">
         <v>1</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="7">
         <f t="shared" si="2"/>
         <v>110000</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="8">
         <f t="shared" si="3"/>
         <v>3010000</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="4">
         <v>2300000</v>
       </c>
     </row>
     <row r="21" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="6">
         <f>SUM(F7:F20)</f>
         <v>41200000</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="6">
         <f t="shared" ref="G21:N21" si="4">SUM(G7:G20)</f>
         <v>81444</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="6">
         <f t="shared" si="4"/>
         <v>3000</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="6">
         <f t="shared" si="4"/>
         <v>458</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="6">
         <f t="shared" si="4"/>
         <v>1374000</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K21" s="6">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="6">
         <f t="shared" si="4"/>
         <v>2200000</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="6">
         <f>F21+J21+L21</f>
         <v>44774000</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N21" s="6">
         <f t="shared" si="4"/>
         <v>38300000</v>
       </c>
     </row>
     <row r="22" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="6">
         <f>SUM(F7:F20)</f>
         <v>41200000</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="6">
         <f t="shared" ref="G22:N22" si="5">SUM(G7:G20)</f>
         <v>81444</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="6">
         <f t="shared" si="5"/>
         <v>3000</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="6">
         <f t="shared" si="5"/>
         <v>458</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="6">
         <f t="shared" si="5"/>
         <v>1374000</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="6">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="6">
         <f t="shared" si="5"/>
         <v>2200000</v>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="6">
         <f t="shared" si="5"/>
         <v>44774000</v>
       </c>
-      <c r="N22" s="8">
+      <c r="N22" s="6">
         <f t="shared" si="5"/>
-        <v>38300000</v>
-      </c>
-    </row>
-    <row r="25" spans="5:14" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="E25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="4"/>
-    </row>
-    <row r="26" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E28" s="5">
-        <v>103</v>
-      </c>
-      <c r="F28" s="9">
-        <v>2500000</v>
-      </c>
-      <c r="G28" s="6">
-        <f>H7</f>
-        <v>3000</v>
-      </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6">
-        <f>IF(H28-G28 &gt; 0, H28-G28, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="9">
-        <f>I28*3000</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="6">
-        <v>1</v>
-      </c>
-      <c r="L28" s="9">
-        <f>K28*110000</f>
-        <v>110000</v>
-      </c>
-      <c r="M28" s="10">
-        <f>F28+J28+L28</f>
-        <v>2610000</v>
-      </c>
-      <c r="N28" s="6">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="29" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E29" s="5">
-        <v>104</v>
-      </c>
-      <c r="F29" s="9">
-        <v>3200000</v>
-      </c>
-      <c r="G29" s="6">
-        <f t="shared" ref="G29:G41" si="6">H8</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6">
-        <f t="shared" ref="I29:I41" si="7">IF(H29-G29 &gt; 0, H29-G29, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="9">
-        <f t="shared" ref="J29:J41" si="8">I29*3000</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="6">
-        <v>1</v>
-      </c>
-      <c r="L29" s="9">
-        <f t="shared" ref="L29:L41" si="9">K29*110000</f>
-        <v>110000</v>
-      </c>
-      <c r="M29" s="10">
-        <f t="shared" ref="M29:M41" si="10">F29+J29+L29</f>
-        <v>3310000</v>
-      </c>
-      <c r="N29" s="6">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="30" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E30" s="5">
-        <v>201</v>
-      </c>
-      <c r="F30" s="9">
-        <v>3000000</v>
-      </c>
-      <c r="G30" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="6">
-        <v>2</v>
-      </c>
-      <c r="L30" s="9">
-        <f t="shared" si="9"/>
-        <v>220000</v>
-      </c>
-      <c r="M30" s="10">
-        <f t="shared" si="10"/>
-        <v>3220000</v>
-      </c>
-      <c r="N30" s="6">
-        <v>2800000</v>
-      </c>
-    </row>
-    <row r="31" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E31" s="5">
-        <v>202</v>
-      </c>
-      <c r="F31" s="9">
-        <v>2800000</v>
-      </c>
-      <c r="G31" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="6">
-        <v>2</v>
-      </c>
-      <c r="L31" s="9">
-        <f t="shared" si="9"/>
-        <v>220000</v>
-      </c>
-      <c r="M31" s="10">
-        <f t="shared" si="10"/>
-        <v>3020000</v>
-      </c>
-      <c r="N31" s="6">
-        <v>2800000</v>
-      </c>
-    </row>
-    <row r="32" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E32" s="5">
-        <v>203</v>
-      </c>
-      <c r="F32" s="9">
-        <v>3000000</v>
-      </c>
-      <c r="G32" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="6">
-        <v>1</v>
-      </c>
-      <c r="L32" s="9">
-        <f t="shared" si="9"/>
-        <v>110000</v>
-      </c>
-      <c r="M32" s="10">
-        <f t="shared" si="10"/>
-        <v>3110000</v>
-      </c>
-      <c r="N32" s="6">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="33" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E33" s="5">
-        <v>204</v>
-      </c>
-      <c r="F33" s="9">
-        <v>3200000</v>
-      </c>
-      <c r="G33" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="6">
-        <v>2</v>
-      </c>
-      <c r="L33" s="9">
-        <f t="shared" si="9"/>
-        <v>220000</v>
-      </c>
-      <c r="M33" s="10">
-        <f t="shared" si="10"/>
-        <v>3420000</v>
-      </c>
-      <c r="N33" s="6">
-        <v>2800000</v>
-      </c>
-    </row>
-    <row r="34" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E34" s="5">
-        <v>301</v>
-      </c>
-      <c r="F34" s="9">
-        <v>3100000</v>
-      </c>
-      <c r="G34" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="6">
-        <v>1</v>
-      </c>
-      <c r="L34" s="9">
-        <f t="shared" si="9"/>
-        <v>110000</v>
-      </c>
-      <c r="M34" s="10">
-        <f t="shared" si="10"/>
-        <v>3210000</v>
-      </c>
-      <c r="N34" s="6">
-        <v>3100000</v>
-      </c>
-    </row>
-    <row r="35" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E35" s="5">
-        <v>302</v>
-      </c>
-      <c r="F35" s="9">
-        <v>2900000</v>
-      </c>
-      <c r="G35" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="6">
-        <v>1</v>
-      </c>
-      <c r="L35" s="9">
-        <f t="shared" si="9"/>
-        <v>110000</v>
-      </c>
-      <c r="M35" s="10">
-        <f t="shared" si="10"/>
-        <v>3010000</v>
-      </c>
-      <c r="N35" s="6">
-        <v>2900000</v>
-      </c>
-    </row>
-    <row r="36" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E36" s="5">
-        <v>303</v>
-      </c>
-      <c r="F36" s="9">
-        <v>3000000</v>
-      </c>
-      <c r="G36" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="6">
-        <v>2</v>
-      </c>
-      <c r="L36" s="9">
-        <f t="shared" si="9"/>
-        <v>220000</v>
-      </c>
-      <c r="M36" s="10">
-        <f t="shared" si="10"/>
-        <v>3220000</v>
-      </c>
-      <c r="N36" s="6">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="37" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E37" s="5">
-        <v>304</v>
-      </c>
-      <c r="F37" s="9">
-        <v>2900000</v>
-      </c>
-      <c r="G37" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="6">
-        <v>1</v>
-      </c>
-      <c r="L37" s="9">
-        <f t="shared" si="9"/>
-        <v>110000</v>
-      </c>
-      <c r="M37" s="10">
-        <f t="shared" si="10"/>
-        <v>3010000</v>
-      </c>
-      <c r="N37" s="6">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="38" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E38" s="5">
-        <v>401</v>
-      </c>
-      <c r="F38" s="9">
-        <v>3000000</v>
-      </c>
-      <c r="G38" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="6">
-        <v>2</v>
-      </c>
-      <c r="L38" s="9">
-        <f t="shared" si="9"/>
-        <v>220000</v>
-      </c>
-      <c r="M38" s="10">
-        <f t="shared" si="10"/>
-        <v>3220000</v>
-      </c>
-      <c r="N38" s="6">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="39" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E39" s="5">
-        <v>402</v>
-      </c>
-      <c r="F39" s="9">
-        <v>2800000</v>
-      </c>
-      <c r="G39" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J39" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K39" s="6">
-        <v>1</v>
-      </c>
-      <c r="L39" s="9">
-        <f t="shared" si="9"/>
-        <v>110000</v>
-      </c>
-      <c r="M39" s="10">
-        <f t="shared" si="10"/>
-        <v>2910000</v>
-      </c>
-      <c r="N39" s="6">
-        <v>2800000</v>
-      </c>
-    </row>
-    <row r="40" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E40" s="5">
-        <v>403</v>
-      </c>
-      <c r="F40" s="9">
-        <v>2900000</v>
-      </c>
-      <c r="G40" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="6">
-        <v>2</v>
-      </c>
-      <c r="L40" s="9">
-        <f t="shared" si="9"/>
-        <v>220000</v>
-      </c>
-      <c r="M40" s="10">
-        <f t="shared" si="10"/>
-        <v>3120000</v>
-      </c>
-      <c r="N40" s="6">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="41" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E41" s="5">
-        <v>404</v>
-      </c>
-      <c r="F41" s="9">
-        <v>2900000</v>
-      </c>
-      <c r="G41" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="6">
-        <v>1</v>
-      </c>
-      <c r="L41" s="9">
-        <f t="shared" si="9"/>
-        <v>110000</v>
-      </c>
-      <c r="M41" s="10">
-        <f t="shared" si="10"/>
-        <v>3010000</v>
-      </c>
-      <c r="N41" s="6">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="42" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E42" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="8">
-        <f>SUM(F28:F41)</f>
-        <v>41200000</v>
-      </c>
-      <c r="G42" s="8">
-        <f t="shared" ref="G42" si="11">SUM(G28:G41)</f>
-        <v>3000</v>
-      </c>
-      <c r="H42" s="8">
-        <f t="shared" ref="H42" si="12">SUM(H28:H41)</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="8">
-        <f t="shared" ref="I42" si="13">SUM(I28:I41)</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="8">
-        <f t="shared" ref="J42" si="14">SUM(J28:J41)</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="8">
-        <f t="shared" ref="K42" si="15">SUM(K28:K41)</f>
-        <v>20</v>
-      </c>
-      <c r="L42" s="8">
-        <f t="shared" ref="L42" si="16">SUM(L28:L41)</f>
-        <v>2200000</v>
-      </c>
-      <c r="M42" s="8">
-        <f>F42+J42+L42</f>
-        <v>43400000</v>
-      </c>
-      <c r="N42" s="8">
-        <f t="shared" ref="N42" si="17">SUM(N28:N41)</f>
-        <v>38300000</v>
-      </c>
-    </row>
-    <row r="43" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="E43" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" s="8">
-        <f>SUM(F28:F41)</f>
-        <v>41200000</v>
-      </c>
-      <c r="G43" s="8">
-        <f t="shared" ref="G43:N43" si="18">SUM(G28:G41)</f>
-        <v>3000</v>
-      </c>
-      <c r="H43" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="8">
-        <f t="shared" si="18"/>
-        <v>20</v>
-      </c>
-      <c r="L43" s="8">
-        <f t="shared" si="18"/>
-        <v>2200000</v>
-      </c>
-      <c r="M43" s="8">
-        <f t="shared" si="18"/>
-        <v>43400000</v>
-      </c>
-      <c r="N43" s="8">
-        <f t="shared" si="18"/>
         <v>38300000</v>
       </c>
     </row>
@@ -1762,19 +1123,13 @@
     <filterColumn colId="4" showButton="0"/>
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
-  <mergeCells count="12">
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N26:N27"/>
+  <mergeCells count="6">
+    <mergeCell ref="E4:M4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
-    <mergeCell ref="E4:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/$/Money.xlsx
+++ b/$/Money.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tro\$\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E309262-BEC0-4CBA-A084-698211731E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895B151F-A9F5-45F1-903E-8560B680E1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,15 +566,15 @@
         <v>2542</v>
       </c>
       <c r="H7" s="4">
-        <v>3000</v>
+        <v>2561</v>
       </c>
       <c r="I7" s="4">
         <f>IF(H7-G7 &gt; 0, H7-G7, 0)</f>
-        <v>458</v>
+        <v>19</v>
       </c>
       <c r="J7" s="7">
         <f>I7*3000</f>
-        <v>1374000</v>
+        <v>57000</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -585,7 +585,7 @@
       </c>
       <c r="M7" s="8">
         <f>F7+J7+L7</f>
-        <v>3984000</v>
+        <v>2667000</v>
       </c>
       <c r="N7" s="4">
         <v>2500000</v>
@@ -601,14 +601,16 @@
       <c r="G8" s="4">
         <v>3736</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="4">
+        <v>3946</v>
+      </c>
       <c r="I8" s="4">
         <f t="shared" ref="I8:I20" si="0">IF(H8-G8 &gt; 0, H8-G8, 0)</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" ref="J8:J20" si="1">I8*3000</f>
-        <v>0</v>
+        <v>630000</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -619,7 +621,7 @@
       </c>
       <c r="M8" s="8">
         <f t="shared" ref="M8:M20" si="3">F8+J8+L8</f>
-        <v>3310000</v>
+        <v>3940000</v>
       </c>
       <c r="N8" s="4">
         <v>3000000</v>
@@ -630,19 +632,21 @@
         <v>201</v>
       </c>
       <c r="F9" s="7">
-        <v>3000000</v>
+        <v>3300000</v>
       </c>
       <c r="G9" s="4">
         <v>5894</v>
       </c>
-      <c r="H9" s="4"/>
+      <c r="H9" s="4">
+        <v>6085</v>
+      </c>
       <c r="I9" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>573000</v>
       </c>
       <c r="K9" s="4">
         <v>2</v>
@@ -653,7 +657,7 @@
       </c>
       <c r="M9" s="8">
         <f t="shared" si="3"/>
-        <v>3220000</v>
+        <v>4093000</v>
       </c>
       <c r="N9" s="4">
         <v>2800000</v>
@@ -669,14 +673,16 @@
       <c r="G10" s="4">
         <v>5826</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="4">
+        <v>5951</v>
+      </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>375000</v>
       </c>
       <c r="K10" s="4">
         <v>2</v>
@@ -687,7 +693,7 @@
       </c>
       <c r="M10" s="8">
         <f t="shared" si="3"/>
-        <v>3020000</v>
+        <v>3395000</v>
       </c>
       <c r="N10" s="4">
         <v>2800000</v>
@@ -703,14 +709,16 @@
       <c r="G11" s="4">
         <v>7113</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="4">
+        <v>7240</v>
+      </c>
       <c r="I11" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>381000</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -721,7 +729,7 @@
       </c>
       <c r="M11" s="8">
         <f t="shared" si="3"/>
-        <v>3110000</v>
+        <v>3491000</v>
       </c>
       <c r="N11" s="4">
         <v>3000000</v>
@@ -737,14 +745,16 @@
       <c r="G12" s="4">
         <v>14308</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="4">
+        <v>14848</v>
+      </c>
       <c r="I12" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="J12" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1620000</v>
       </c>
       <c r="K12" s="4">
         <v>2</v>
@@ -755,7 +765,7 @@
       </c>
       <c r="M12" s="8">
         <f t="shared" si="3"/>
-        <v>3420000</v>
+        <v>5040000</v>
       </c>
       <c r="N12" s="4">
         <v>2800000</v>
@@ -771,14 +781,16 @@
       <c r="G13" s="4">
         <v>6034</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="4">
+        <v>6286</v>
+      </c>
       <c r="I13" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="J13" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>756000</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -789,7 +801,7 @@
       </c>
       <c r="M13" s="8">
         <f t="shared" si="3"/>
-        <v>3210000</v>
+        <v>3966000</v>
       </c>
       <c r="N13" s="4">
         <v>3100000</v>
@@ -805,14 +817,16 @@
       <c r="G14" s="4">
         <v>6821</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="4">
+        <v>6985</v>
+      </c>
       <c r="I14" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="J14" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>492000</v>
       </c>
       <c r="K14" s="4">
         <v>1</v>
@@ -823,7 +837,7 @@
       </c>
       <c r="M14" s="8">
         <f t="shared" si="3"/>
-        <v>3010000</v>
+        <v>3502000</v>
       </c>
       <c r="N14" s="4">
         <v>2900000</v>
@@ -839,14 +853,16 @@
       <c r="G15" s="4">
         <v>7758</v>
       </c>
-      <c r="H15" s="4"/>
+      <c r="H15" s="4">
+        <v>7980</v>
+      </c>
       <c r="I15" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="J15" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>666000</v>
       </c>
       <c r="K15" s="4">
         <v>2</v>
@@ -857,7 +873,7 @@
       </c>
       <c r="M15" s="8">
         <f t="shared" si="3"/>
-        <v>3220000</v>
+        <v>3886000</v>
       </c>
       <c r="N15" s="4">
         <v>3000000</v>
@@ -868,19 +884,21 @@
         <v>304</v>
       </c>
       <c r="F16" s="7">
-        <v>2900000</v>
+        <v>3200000</v>
       </c>
       <c r="G16" s="4">
         <v>6688</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="4">
+        <v>6768</v>
+      </c>
       <c r="I16" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J16" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="K16" s="4">
         <v>1</v>
@@ -891,10 +909,10 @@
       </c>
       <c r="M16" s="8">
         <f t="shared" si="3"/>
-        <v>3010000</v>
+        <v>3550000</v>
       </c>
       <c r="N16" s="4">
-        <v>2500000</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="17" spans="5:14" x14ac:dyDescent="0.25">
@@ -907,14 +925,16 @@
       <c r="G17" s="4">
         <v>1763</v>
       </c>
-      <c r="H17" s="4"/>
+      <c r="H17" s="4">
+        <v>2182</v>
+      </c>
       <c r="I17" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1257000</v>
       </c>
       <c r="K17" s="4">
         <v>2</v>
@@ -925,7 +945,7 @@
       </c>
       <c r="M17" s="8">
         <f t="shared" si="3"/>
-        <v>3220000</v>
+        <v>4477000</v>
       </c>
       <c r="N17" s="4">
         <v>2500000</v>
@@ -941,14 +961,16 @@
       <c r="G18" s="4">
         <v>5359</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="4">
+        <v>5474</v>
+      </c>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J18" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>345000</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
@@ -959,7 +981,7 @@
       </c>
       <c r="M18" s="8">
         <f t="shared" si="3"/>
-        <v>2910000</v>
+        <v>3255000</v>
       </c>
       <c r="N18" s="4">
         <v>2800000</v>
@@ -975,14 +997,16 @@
       <c r="G19" s="4">
         <v>609</v>
       </c>
-      <c r="H19" s="4"/>
+      <c r="H19" s="4">
+        <v>755</v>
+      </c>
       <c r="I19" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>438000</v>
       </c>
       <c r="K19" s="4">
         <v>2</v>
@@ -993,7 +1017,7 @@
       </c>
       <c r="M19" s="8">
         <f t="shared" si="3"/>
-        <v>3120000</v>
+        <v>3558000</v>
       </c>
       <c r="N19" s="4">
         <v>2300000</v>
@@ -1009,14 +1033,16 @@
       <c r="G20" s="4">
         <v>6993</v>
       </c>
-      <c r="H20" s="4"/>
+      <c r="H20" s="4">
+        <v>7160</v>
+      </c>
       <c r="I20" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>501000</v>
       </c>
       <c r="K20" s="4">
         <v>1</v>
@@ -1027,7 +1053,7 @@
       </c>
       <c r="M20" s="8">
         <f t="shared" si="3"/>
-        <v>3010000</v>
+        <v>3511000</v>
       </c>
       <c r="N20" s="4">
         <v>2300000</v>
@@ -1039,7 +1065,7 @@
       </c>
       <c r="F21" s="6">
         <f>SUM(F7:F20)</f>
-        <v>41200000</v>
+        <v>41800000</v>
       </c>
       <c r="G21" s="6">
         <f t="shared" ref="G21:N21" si="4">SUM(G7:G20)</f>
@@ -1047,15 +1073,15 @@
       </c>
       <c r="H21" s="6">
         <f t="shared" si="4"/>
-        <v>3000</v>
+        <v>84221</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="4"/>
-        <v>458</v>
+        <v>2777</v>
       </c>
       <c r="J21" s="6">
         <f t="shared" si="4"/>
-        <v>1374000</v>
+        <v>8331000</v>
       </c>
       <c r="K21" s="6">
         <f t="shared" si="4"/>
@@ -1067,11 +1093,11 @@
       </c>
       <c r="M21" s="6">
         <f>F21+J21+L21</f>
-        <v>44774000</v>
+        <v>52331000</v>
       </c>
       <c r="N21" s="6">
         <f t="shared" si="4"/>
-        <v>38300000</v>
+        <v>39000000</v>
       </c>
     </row>
     <row r="22" spans="5:14" x14ac:dyDescent="0.25">
@@ -1080,7 +1106,7 @@
       </c>
       <c r="F22" s="6">
         <f>SUM(F7:F20)</f>
-        <v>41200000</v>
+        <v>41800000</v>
       </c>
       <c r="G22" s="6">
         <f t="shared" ref="G22:N22" si="5">SUM(G7:G20)</f>
@@ -1088,15 +1114,15 @@
       </c>
       <c r="H22" s="6">
         <f t="shared" si="5"/>
-        <v>3000</v>
+        <v>84221</v>
       </c>
       <c r="I22" s="6">
         <f t="shared" si="5"/>
-        <v>458</v>
+        <v>2777</v>
       </c>
       <c r="J22" s="6">
         <f t="shared" si="5"/>
-        <v>1374000</v>
+        <v>8331000</v>
       </c>
       <c r="K22" s="6">
         <f t="shared" si="5"/>
@@ -1108,11 +1134,11 @@
       </c>
       <c r="M22" s="6">
         <f t="shared" si="5"/>
-        <v>44774000</v>
+        <v>52331000</v>
       </c>
       <c r="N22" s="6">
         <f t="shared" si="5"/>
-        <v>38300000</v>
+        <v>39000000</v>
       </c>
     </row>
   </sheetData>
@@ -1124,12 +1150,12 @@
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
   <mergeCells count="6">
+    <mergeCell ref="N5:N6"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
